--- a/artfynd/A 30060-2022 artfynd.xlsx
+++ b/artfynd/A 30060-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30060-2022 artfynd.xlsx
+++ b/artfynd/A 30060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104036147</v>
+        <v>104036146</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473180.6267025439</v>
+        <v>473164</v>
       </c>
       <c r="R2" t="n">
-        <v>7012023.595928025</v>
+        <v>7012023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104036149</v>
+        <v>104036147</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Acksjön nv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473182.581973678</v>
+        <v>473180</v>
       </c>
       <c r="R3" t="n">
-        <v>7012041.609299188</v>
+        <v>7012024</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,24 +840,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +866,323 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104036155</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Acksjön nv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>473157</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7011953</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104036148</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Acksjön nv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>473161</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012020</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104036149</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Acksjön nv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>473182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012042</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30060-2022 artfynd.xlsx
+++ b/artfynd/A 30060-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036146</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036148</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,8 +1208,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036149</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>